--- a/transportation_request_forms/038_mobility_allowance_request_form--transportation_request_forms.xlsx
+++ b/transportation_request_forms/038_mobility_allowance_request_form--transportation_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'wheelchair',_'text':_'wheelchair'}</t>
+          <t>wheelchair</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Wheelchair', 'text': 'Wheelchair'}</t>
+          <t>Wheelchair</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'scooter',_'text':_'scooter'}</t>
+          <t>scooter</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Scooter', 'text': 'Scooter'}</t>
+          <t>Scooter</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily',_'text':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Daily', 'text': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'weekly',_'text':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Weekly', 'text': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monthly',_'text':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Monthly', 'text': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'less_than_30_days',_'text':_'less_than_30_days'}</t>
+          <t>less_than_30_days</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Less than 30 days', 'text': 'Less than 30 days'}</t>
+          <t>Less than 30 days</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'1-3_months',_'text':_'1-3_months'}</t>
+          <t>1-3_months</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '1-3 months', 'text': '1-3 months'}</t>
+          <t>1-3 months</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'6-12_months',_'text':_'6-12_months'}</t>
+          <t>6-12_months</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '6-12 months', 'text': '6-12 months'}</t>
+          <t>6-12 months</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'more_than_1_year',_'text':_'more_than_1_year'}</t>
+          <t>more_than_1_year</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'More than 1 year', 'text': 'More than 1 year'}</t>
+          <t>More than 1 year</t>
         </is>
       </c>
     </row>
